--- a/Team-Data/2007-08/1-5-2007-08.xlsx
+++ b/Team-Data/2007-08/1-5-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="J2" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="M2" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.312</v>
+        <v>0.319</v>
       </c>
       <c r="O2" t="n">
         <v>22.5</v>
       </c>
       <c r="P2" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
         <v>11.8</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U2" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="V2" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X2" t="n">
         <v>5.5</v>
@@ -727,28 +794,28 @@
         <v>5.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.7</v>
+        <v>94.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>4</v>
@@ -760,37 +827,37 @@
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM2" t="n">
         <v>29</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
         <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AV2" t="n">
         <v>18</v>
@@ -811,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.906</v>
+        <v>0.903</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J3" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.2</v>
+        <v>100.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>21</v>
@@ -942,10 +1009,10 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM3" t="n">
         <v>10</v>
@@ -954,25 +1021,25 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
@@ -984,7 +1051,7 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
@@ -1124,7 +1191,7 @@
         <v>24</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>14</v>
@@ -1133,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1157,22 +1224,22 @@
         <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
         <v>10</v>
       </c>
       <c r="AX4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
         <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.406</v>
+        <v>0.387</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.417</v>
+        <v>0.419</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
         <v>0.327</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.76</v>
+        <v>0.762</v>
       </c>
       <c r="R5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T5" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1267,25 +1334,25 @@
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
         <v>93.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1300,31 +1367,31 @@
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>3</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1342,22 +1409,22 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>-3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>17</v>
@@ -1485,7 +1552,7 @@
         <v>23</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1497,10 +1564,10 @@
         <v>13</v>
       </c>
       <c r="AN6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO6" t="n">
         <v>19</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1533,7 +1600,7 @@
         <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA6" t="n">
         <v>25</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1649,16 +1716,16 @@
         <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF7" t="n">
         <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
         <v>22</v>
@@ -1667,7 +1734,7 @@
         <v>16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
         <v>6</v>
@@ -1676,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="AM7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN7" t="n">
         <v>12</v>
@@ -1694,10 +1761,10 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>17</v>
@@ -1724,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>3.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.765</v>
+        <v>0.788</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J9" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.468</v>
+        <v>0.47</v>
       </c>
       <c r="L9" t="n">
         <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O9" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P9" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R9" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S9" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
         <v>23.6</v>
       </c>
       <c r="V9" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -1998,22 +2065,22 @@
         <v>5.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.59999999999999</v>
+        <v>100.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2043,16 +2110,16 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
@@ -2061,7 +2128,7 @@
         <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
@@ -2073,19 +2140,19 @@
         <v>19</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2231,7 +2298,7 @@
         <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>20</v>
@@ -2240,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2249,16 +2316,16 @@
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>81.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L11" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
         <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R11" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S11" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
       <c r="U11" t="n">
         <v>20.7</v>
@@ -2359,43 +2426,43 @@
         <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI11" t="n">
         <v>19</v>
       </c>
-      <c r="AI11" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>24</v>
@@ -2413,22 +2480,22 @@
         <v>27</v>
       </c>
       <c r="AP11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2443,10 +2510,10 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-0.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
         <v>19</v>
@@ -2571,7 +2638,7 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2592,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2616,7 +2683,7 @@
         <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2762,7 +2829,7 @@
         <v>19</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
         <v>25</v>
@@ -2777,10 +2844,10 @@
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>24</v>
@@ -2810,7 +2877,7 @@
         <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
         <v>30</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
@@ -2962,7 +3029,7 @@
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
@@ -2983,22 +3050,22 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
@@ -3150,16 +3217,16 @@
         <v>27</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>29</v>
@@ -3168,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3180,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
@@ -3299,7 +3366,7 @@
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>24</v>
@@ -3308,7 +3375,7 @@
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3323,13 +3390,13 @@
         <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS16" t="n">
         <v>21</v>
@@ -3347,7 +3414,7 @@
         <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>5</v>
@@ -3496,7 +3563,7 @@
         <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN17" t="n">
         <v>23</v>
@@ -3511,13 +3578,13 @@
         <v>22</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
         <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3535,13 +3602,13 @@
         <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,7 +3745,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J19" t="n">
         <v>76.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.323</v>
+        <v>0.317</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="P19" t="n">
-        <v>29</v>
+        <v>28.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.73</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
         <v>11.3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
         <v>41.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
       </c>
       <c r="W19" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z19" t="n">
         <v>23.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,19 +3927,19 @@
         <v>22</v>
       </c>
       <c r="AM19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3887,28 +3954,28 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
         <v>29</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -3937,70 +4004,70 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M20" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O20" t="n">
         <v>15.9</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0.793</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="T20" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U20" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
         <v>7.9</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Z20" t="n">
         <v>19.4</v>
@@ -4009,16 +4076,16 @@
         <v>19.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>97.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4027,19 +4094,19 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL20" t="n">
         <v>8</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>7</v>
@@ -4060,13 +4127,13 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4078,7 +4145,7 @@
         <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
         <v>3</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J21" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L21" t="n">
         <v>5.5</v>
@@ -4149,67 +4216,67 @@
         <v>16.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.326</v>
       </c>
       <c r="O21" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P21" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="n">
         <v>0.707</v>
       </c>
       <c r="R21" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S21" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
         <v>16.8</v>
       </c>
       <c r="V21" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W21" t="n">
         <v>6.7</v>
       </c>
       <c r="X21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
         <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4227,13 +4294,13 @@
         <v>19</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
       </c>
       <c r="AP21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
         <v>28</v>
@@ -4242,7 +4309,7 @@
         <v>2</v>
       </c>
       <c r="AS21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
@@ -4251,25 +4318,25 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ21" t="n">
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>9</v>
@@ -4412,7 +4479,7 @@
         <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4442,7 +4509,7 @@
         <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
@@ -4576,7 +4643,7 @@
         <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
         <v>18</v>
@@ -4603,16 +4670,16 @@
         <v>26</v>
       </c>
       <c r="AR23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT23" t="n">
         <v>17</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4624,13 +4691,13 @@
         <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.697</v>
+        <v>0.719</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="J24" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.492</v>
+        <v>0.491</v>
       </c>
       <c r="L24" t="n">
         <v>8.300000000000001</v>
@@ -4695,37 +4762,37 @@
         <v>22.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O24" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P24" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="V24" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y24" t="n">
         <v>3.8</v>
@@ -4737,22 +4804,22 @@
         <v>19.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.3</v>
+        <v>109.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
       </c>
       <c r="AF24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -4761,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4779,10 +4846,10 @@
         <v>24</v>
       </c>
       <c r="AP24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4800,7 +4867,7 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -4847,70 +4914,70 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
         <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0.618</v>
+        <v>0.606</v>
       </c>
       <c r="H25" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I25" t="n">
         <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>77.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
         <v>6.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="O25" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T25" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U25" t="n">
         <v>21.7</v>
       </c>
       <c r="V25" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
         <v>19.9</v>
@@ -4919,13 +4986,13 @@
         <v>21.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4937,16 +5004,16 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL25" t="n">
         <v>12</v>
@@ -4958,19 +5025,19 @@
         <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AP25" t="n">
         <v>21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4994,7 +5061,7 @@
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.375</v>
+        <v>0.387</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5047,19 +5114,19 @@
         <v>35.3</v>
       </c>
       <c r="J26" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M26" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O26" t="n">
         <v>21.3</v>
@@ -5068,58 +5135,58 @@
         <v>27.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S26" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T26" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U26" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="W26" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
@@ -5137,7 +5204,7 @@
         <v>21</v>
       </c>
       <c r="AN26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5152,7 +5219,7 @@
         <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5170,16 +5237,16 @@
         <v>28</v>
       </c>
       <c r="AY26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA26" t="n">
         <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>6.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5334,13 +5401,13 @@
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
@@ -5483,13 +5550,13 @@
         <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
@@ -5504,16 +5571,16 @@
         <v>13</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5540,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -5653,28 +5720,28 @@
         <v>1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5716,7 +5783,7 @@
         <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>7</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
         <v>18</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.514</v>
+        <v>0.529</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.49</v>
@@ -5787,64 +5854,64 @@
         <v>10.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.748</v>
       </c>
       <c r="R30" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="T30" t="n">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.5</v>
+        <v>104.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5859,7 +5926,7 @@
         <v>2</v>
       </c>
       <c r="AL30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM30" t="n">
         <v>30</v>
@@ -5868,16 +5935,16 @@
         <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>30</v>
@@ -5895,7 +5962,7 @@
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY30" t="n">
         <v>29</v>
@@ -5904,13 +5971,13 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
@@ -6017,22 +6084,22 @@
         <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
         <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>10</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
         <v>13</v>
@@ -6062,19 +6129,19 @@
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6089,7 +6156,7 @@
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-5-2007-08</t>
+          <t>2008-01-05</t>
         </is>
       </c>
     </row>
